--- a/reports/Planters_in_Malls_Details_2026.xlsx
+++ b/reports/Planters_in_Malls_Details_2026.xlsx
@@ -12,7 +12,16 @@
     <sheet name="Mall Planters" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Planter Photo Reference" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'RC &amp; IR Lobbies'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'RC &amp; IR Lobbies'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FP Lobbies'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'FP Lobbies'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mall Planters'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Mall Planters'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planter Photo Reference'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Planter Photo Reference'!$A$1:$D$27</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -202,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,15 +266,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,8 +515,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <row>2</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -540,8 +540,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -565,8 +565,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -590,8 +590,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -615,8 +615,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
+      <row>6</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -640,8 +640,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
+      <row>7</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -665,8 +665,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
+      <row>8</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -690,8 +690,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
+      <row>9</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -715,8 +715,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
+      <row>10</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -740,8 +740,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
+      <row>11</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -765,8 +765,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
+      <row>12</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -790,8 +790,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
+      <row>13</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -815,8 +815,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
+      <row>14</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -840,8 +840,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
+      <row>15</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -865,8 +865,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
+      <row>16</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -890,8 +890,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
+      <row>17</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -915,8 +915,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
+      <row>18</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -940,8 +940,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
+      <row>19</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -965,8 +965,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
+      <row>20</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -990,8 +990,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
+      <row>21</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1015,8 +1015,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
+      <row>22</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1040,8 +1040,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
+      <row>23</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1065,8 +1065,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
+      <row>24</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1090,8 +1090,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
+      <row>25</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1115,8 +1115,8 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
+      <row>26</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="1219200" cy="1381125"/>
     <pic>
@@ -1426,7 +1426,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1766,6 +1766,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1774,7 +1775,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2062,6 +2063,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2070,7 +2072,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2898,6 +2900,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2906,335 +2909,404 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.45" customWidth="1" min="1" max="1"/>
     <col width="26.45" customWidth="1" min="2" max="2"/>
     <col width="22.45" customWidth="1" min="3" max="3"/>
+    <col width="24.45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="37.4" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Source sheet</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Shown at</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="115" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="37.4" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>RC &amp; IR Lobbies</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>cell B3</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="115" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>cell B4</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="115" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="115" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>cell B19</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="115" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="115" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>FP Lobbies</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>cell B20</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="115" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="115" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Extra large - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="115" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="115" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Big - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="115" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="115" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Small - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="115" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="115" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Medum - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="115" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="115" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Extra large - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="115" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="115" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Big - GF block</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="115" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="115" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Extra large - FF block</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="115" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="115" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Medum - FF block</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="115" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="115" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Small - FF block</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="115" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="115" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Big - FF block</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="115" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="115" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Extra large - SF block</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="115" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="115" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Big - SF block</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="115" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="115" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Medum - SF block</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="115" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="115" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Small - SF block</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="115" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="115" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Big - header</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="115" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="115" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Medum - header</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="115" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="115" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Big - header</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="115" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="115" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Small - header</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="115" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="115" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Medum - header</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="115" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="115" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Small - MLB</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="115" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="115" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Mall</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Big - header</t>
         </is>
       </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>